--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -724,6 +724,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -733,7 +736,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -894,6 +897,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -937,7 +943,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1099,6 +1105,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1108,7 +1117,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1270,6 +1279,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13918241.906652076</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14227459.764016345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1312,7 +1324,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1474,6 +1486,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1483,7 +1498,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1645,6 +1660,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4556907.088924652</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4866124.9462889209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1666,11 +1684,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443506688"/>
-        <c:axId val="443508608"/>
+        <c:axId val="437242112"/>
+        <c:axId val="447631360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443506688"/>
+        <c:axId val="437242112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1713,14 +1731,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443508608"/>
+        <c:crossAx val="447631360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443508608"/>
+        <c:axId val="447631360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1771,7 +1789,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443506688"/>
+        <c:crossAx val="437242112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1932,7 +1950,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2094,6 +2112,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-73556.079313855051</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-244188.52262430632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2108,8 +2129,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="467802368"/>
-        <c:axId val="467800832"/>
+        <c:axId val="452622976"/>
+        <c:axId val="452621440"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2134,7 +2155,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2296,6 +2317,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2305,7 +2329,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2467,6 +2491,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2483,11 +2510,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443540992"/>
-        <c:axId val="443542528"/>
+        <c:axId val="452609920"/>
+        <c:axId val="452611456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443540992"/>
+        <c:axId val="452609920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2530,14 +2557,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443542528"/>
+        <c:crossAx val="452611456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443542528"/>
+        <c:axId val="452611456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2588,12 +2615,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443540992"/>
+        <c:crossAx val="452609920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="467800832"/>
+        <c:axId val="452621440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2630,12 +2657,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467802368"/>
+        <c:crossAx val="452622976"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="467802368"/>
+        <c:axId val="452622976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,7 +2671,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="467800832"/>
+        <c:crossAx val="452621440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2776,7 +2803,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2938,6 +2965,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2952,8 +2982,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="469383424"/>
-        <c:axId val="469381120"/>
+        <c:axId val="561720320"/>
+        <c:axId val="561718400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2978,7 +3008,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3140,6 +3170,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3149,7 +3182,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3311,6 +3344,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3327,11 +3363,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469369216"/>
-        <c:axId val="469370752"/>
+        <c:axId val="559890816"/>
+        <c:axId val="559893120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469369216"/>
+        <c:axId val="559890816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3374,14 +3410,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469370752"/>
+        <c:crossAx val="559893120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="469370752"/>
+        <c:axId val="559893120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3432,12 +3468,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469369216"/>
+        <c:crossAx val="559890816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="469381120"/>
+        <c:axId val="561718400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3474,12 +3510,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469383424"/>
+        <c:crossAx val="561720320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="469383424"/>
+        <c:axId val="561720320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3488,7 +3524,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="469381120"/>
+        <c:crossAx val="561718400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3638,7 +3674,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3800,6 +3836,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3809,7 +3848,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3970,6 +4009,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4013,7 +4055,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4175,6 +4217,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4184,7 +4229,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4346,6 +4391,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14963307.508744044</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15294247.764746865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4388,7 +4436,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4550,6 +4598,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4559,7 +4610,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4721,6 +4772,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4955533.9692211729</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5286474.2252239939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4742,11 +4796,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="476358912"/>
-        <c:axId val="507683200"/>
+        <c:axId val="655437824"/>
+        <c:axId val="655439360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="476358912"/>
+        <c:axId val="655437824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4789,14 +4843,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="507683200"/>
+        <c:crossAx val="655439360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="507683200"/>
+        <c:axId val="655439360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4847,7 +4901,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476358912"/>
+        <c:crossAx val="655437824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5008,7 +5062,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5170,6 +5224,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-76300.054631715335</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-131316.53344699508</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5184,8 +5241,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="536819200"/>
-        <c:axId val="536817664"/>
+        <c:axId val="433459200"/>
+        <c:axId val="691362048"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5210,7 +5267,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5372,6 +5429,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5381,7 +5441,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5543,6 +5603,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5559,11 +5622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535826816"/>
-        <c:axId val="535828736"/>
+        <c:axId val="689166976"/>
+        <c:axId val="691360128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535826816"/>
+        <c:axId val="689166976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5606,14 +5669,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535828736"/>
+        <c:crossAx val="691360128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535828736"/>
+        <c:axId val="691360128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5664,12 +5727,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535826816"/>
+        <c:crossAx val="689166976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="536817664"/>
+        <c:axId val="691362048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5706,12 +5769,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536819200"/>
+        <c:crossAx val="433459200"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="536819200"/>
+        <c:axId val="433459200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5720,7 +5783,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="536817664"/>
+        <c:crossAx val="691362048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5870,7 +5933,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6032,6 +6095,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6041,7 +6107,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6202,6 +6268,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6245,7 +6314,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6407,6 +6476,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6416,7 +6488,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6578,6 +6650,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14844133.861885205</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15173385.354710398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6620,7 +6695,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6782,6 +6857,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6791,7 +6869,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6953,6 +7031,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4881348.482635295</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5210599.9754604883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6974,11 +7055,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99506816"/>
-        <c:axId val="99508608"/>
+        <c:axId val="433511424"/>
+        <c:axId val="433513216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99506816"/>
+        <c:axId val="433511424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7021,14 +7102,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99508608"/>
+        <c:crossAx val="433513216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99508608"/>
+        <c:axId val="433513216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7079,7 +7160,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99506816"/>
+        <c:crossAx val="433511424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7240,7 +7321,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7402,6 +7483,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7416,8 +7500,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="99532160"/>
-        <c:axId val="99530624"/>
+        <c:axId val="437153792"/>
+        <c:axId val="437152000"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7442,7 +7526,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7604,6 +7688,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7613,7 +7700,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7775,6 +7862,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7791,11 +7881,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99523200"/>
-        <c:axId val="99529088"/>
+        <c:axId val="437144576"/>
+        <c:axId val="437150464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99523200"/>
+        <c:axId val="437144576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7838,14 +7928,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99529088"/>
+        <c:crossAx val="437150464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99529088"/>
+        <c:axId val="437150464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7896,12 +7986,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99523200"/>
+        <c:crossAx val="437144576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="99530624"/>
+        <c:axId val="437152000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7938,12 +8028,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99532160"/>
+        <c:crossAx val="437153792"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="99532160"/>
+        <c:axId val="437153792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7952,7 +8042,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="99530624"/>
+        <c:crossAx val="437152000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8102,7 +8192,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8264,6 +8354,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8273,7 +8366,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8434,6 +8527,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8477,7 +8573,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8639,6 +8735,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8648,7 +8747,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8810,6 +8909,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>132401493.54502271</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>135374422.21281305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8852,7 +8954,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9014,6 +9116,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9023,7 +9128,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9185,6 +9290,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>44961540.882420003</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>47934469.550210342</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9206,11 +9314,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99547776"/>
-        <c:axId val="160891264"/>
+        <c:axId val="437181440"/>
+        <c:axId val="437183232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99547776"/>
+        <c:axId val="437181440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9253,14 +9361,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160891264"/>
+        <c:crossAx val="437183232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160891264"/>
+        <c:axId val="437183232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9311,7 +9419,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99547776"/>
+        <c:crossAx val="437181440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9472,7 +9580,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9634,6 +9742,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>123871776.79126592</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>123330440.59734799</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9648,8 +9759,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="440486528"/>
-        <c:axId val="440484992"/>
+        <c:axId val="447753216"/>
+        <c:axId val="447751680"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9674,7 +9785,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9836,6 +9947,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9845,7 +9959,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10007,6 +10121,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10023,11 +10140,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440473472"/>
-        <c:axId val="440475008"/>
+        <c:axId val="447744256"/>
+        <c:axId val="447750144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440473472"/>
+        <c:axId val="447744256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10070,14 +10187,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440475008"/>
+        <c:crossAx val="447750144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440475008"/>
+        <c:axId val="447750144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10128,12 +10245,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440473472"/>
+        <c:crossAx val="447744256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="440484992"/>
+        <c:axId val="447751680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10170,12 +10287,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440486528"/>
+        <c:crossAx val="447753216"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="440486528"/>
+        <c:axId val="447753216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10184,7 +10301,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="440484992"/>
+        <c:crossAx val="447751680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10334,7 +10451,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10496,6 +10613,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10505,7 +10625,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10666,6 +10786,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -10709,7 +10832,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10871,6 +10994,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10880,7 +11006,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11042,6 +11168,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>136510246.47001591</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>139607183.83490777</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11084,7 +11213,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11246,6 +11375,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11255,7 +11387,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11417,6 +11549,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>52929250.134395897</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>56026187.499287754</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11438,11 +11573,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443512704"/>
-        <c:axId val="443514240"/>
+        <c:axId val="452593920"/>
+        <c:axId val="452595712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443512704"/>
+        <c:axId val="452593920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11485,14 +11620,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443514240"/>
+        <c:crossAx val="452595712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443514240"/>
+        <c:axId val="452595712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11543,7 +11678,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443512704"/>
+        <c:crossAx val="452593920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12257,7 +12392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -14672,6 +14807,44 @@
         <v>518829.06704185653</v>
       </c>
     </row>
+    <row r="57" spans="1:12" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="15">
+        <v>12781203.118754858</v>
+      </c>
+      <c r="H57" s="15">
+        <v>13599200.252435327</v>
+      </c>
+      <c r="I57" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J57" s="15">
+        <v>14227459.764016345</v>
+      </c>
+      <c r="K57" s="15">
+        <v>4866124.9462889209</v>
+      </c>
+      <c r="L57" s="14">
+        <v>628259.51158101915</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -14688,7 +14861,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18395,6 +18568,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="57" spans="1:21" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-131316.53344699508</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-123417.79337621325</v>
+      </c>
+      <c r="G57" s="15">
+        <v>13665731.59556484</v>
+      </c>
+      <c r="H57" s="15">
+        <v>14540338.561040219</v>
+      </c>
+      <c r="I57" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J57" s="15">
+        <v>15294247.764746865</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5286474.2252239939</v>
+      </c>
+      <c r="L57" s="14">
+        <v>753909.20370664692</v>
+      </c>
+      <c r="M57" s="23">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="N57" s="23">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="O57" s="23">
+        <v>1.0713333288828533</v>
+      </c>
+      <c r="P57" s="23">
+        <v>0.88464285929997755</v>
+      </c>
+      <c r="Q57" s="23">
+        <v>0.18669046958287572</v>
+      </c>
+      <c r="R57" s="23">
+        <v>0.10844557342075166</v>
+      </c>
+      <c r="S57" s="9">
+        <v>1.6266836013112747E-3</v>
+      </c>
+      <c r="T57" s="9">
+        <v>114.76753649719217</v>
+      </c>
+      <c r="U57" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -18411,7 +18649,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21139,6 +21377,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="15">
+        <v>13615936.237991611</v>
+      </c>
+      <c r="H57" s="15">
+        <v>14487356.300059929</v>
+      </c>
+      <c r="I57" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J57" s="15">
+        <v>15173385.354710398</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5210599.9754604883</v>
+      </c>
+      <c r="L57" s="14">
+        <v>686029.05465046817</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -21155,7 +21437,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23883,6 +24165,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-575981.71600752324</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-541336.19391793292</v>
+      </c>
+      <c r="G57" s="15">
+        <v>123330440.59734799</v>
+      </c>
+      <c r="H57" s="15">
+        <v>131223590.08936608</v>
+      </c>
+      <c r="I57" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J57" s="15">
+        <v>135374422.21281305</v>
+      </c>
+      <c r="K57" s="15">
+        <v>47934469.550210342</v>
+      </c>
+      <c r="L57" s="14">
+        <v>4150832.1234469572</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23899,7 +24225,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26959,6 +27285,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:16" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="14">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="14">
+        <v>-244188.52262430632</v>
+      </c>
+      <c r="H57" s="15">
+        <v>-229500.48892551727</v>
+      </c>
+      <c r="I57" s="15">
+        <v>128809294.87697572</v>
+      </c>
+      <c r="J57" s="15">
+        <v>137053091.10036543</v>
+      </c>
+      <c r="K57" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L57" s="15">
+        <v>139607183.83490777</v>
+      </c>
+      <c r="M57" s="15">
+        <v>56026187.499287754</v>
+      </c>
+      <c r="N57" s="14">
+        <v>2554092.7345423289</v>
+      </c>
+      <c r="O57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="P57" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -727,6 +727,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -736,7 +739,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -900,6 +903,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -943,7 +949,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1108,6 +1114,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1117,7 +1126,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1282,6 +1291,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14227459.764016345</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14329709.596181171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1324,7 +1336,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1489,6 +1501,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1498,7 +1513,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1663,6 +1678,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4866124.9462889209</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4968374.7784537468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1684,11 +1702,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437242112"/>
-        <c:axId val="447631360"/>
+        <c:axId val="493797376"/>
+        <c:axId val="493800064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437242112"/>
+        <c:axId val="493797376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1731,14 +1749,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447631360"/>
+        <c:crossAx val="493800064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447631360"/>
+        <c:axId val="493800064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1789,7 +1807,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437242112"/>
+        <c:crossAx val="493797376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1950,7 +1968,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2115,6 +2133,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-244188.52262430632</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-637497.67999171233</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2129,8 +2150,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="452622976"/>
-        <c:axId val="452621440"/>
+        <c:axId val="529598336"/>
+        <c:axId val="529596800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2155,7 +2176,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2320,6 +2341,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2329,7 +2353,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2494,6 +2518,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,11 +2537,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="452609920"/>
-        <c:axId val="452611456"/>
+        <c:axId val="529581184"/>
+        <c:axId val="529582720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="452609920"/>
+        <c:axId val="529581184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2557,14 +2584,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452611456"/>
+        <c:crossAx val="529582720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="452611456"/>
+        <c:axId val="529582720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2615,12 +2642,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452609920"/>
+        <c:crossAx val="529581184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="452621440"/>
+        <c:axId val="529596800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2657,12 +2684,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452622976"/>
+        <c:crossAx val="529598336"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="452622976"/>
+        <c:axId val="529598336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2671,7 +2698,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="452621440"/>
+        <c:crossAx val="529596800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2803,7 +2830,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2968,6 +2995,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2982,8 +3012,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="561720320"/>
-        <c:axId val="561718400"/>
+        <c:axId val="557295488"/>
+        <c:axId val="557293952"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3008,7 +3038,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3173,6 +3203,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3182,7 +3215,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3347,6 +3380,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3363,11 +3399,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559890816"/>
-        <c:axId val="559893120"/>
+        <c:axId val="543789824"/>
+        <c:axId val="543791744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559890816"/>
+        <c:axId val="543789824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3410,14 +3446,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559893120"/>
+        <c:crossAx val="543791744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559893120"/>
+        <c:axId val="543791744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3468,12 +3504,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559890816"/>
+        <c:crossAx val="543789824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="561718400"/>
+        <c:axId val="557293952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3510,12 +3546,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="561720320"/>
+        <c:crossAx val="557295488"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="561720320"/>
+        <c:axId val="557295488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3524,7 +3560,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="561718400"/>
+        <c:crossAx val="557293952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3674,7 +3710,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3839,6 +3875,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3848,7 +3887,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4012,6 +4051,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4055,7 +4097,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4220,6 +4262,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4229,7 +4274,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4394,6 +4439,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15294247.764746865</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15403573.839066558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4436,7 +4484,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4601,6 +4649,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4610,7 +4661,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4775,6 +4826,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5286474.2252239939</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5395800.2995436862</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4796,11 +4850,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="655437824"/>
-        <c:axId val="655439360"/>
+        <c:axId val="609127808"/>
+        <c:axId val="610740480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="655437824"/>
+        <c:axId val="609127808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4843,14 +4897,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="655439360"/>
+        <c:crossAx val="610740480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="655439360"/>
+        <c:axId val="610740480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4901,7 +4955,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="655437824"/>
+        <c:crossAx val="609127808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5062,7 +5116,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5227,6 +5281,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-131316.53344699508</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5241,8 +5298,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="433459200"/>
-        <c:axId val="691362048"/>
+        <c:axId val="97844224"/>
+        <c:axId val="97842688"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5267,7 +5324,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5432,6 +5489,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5441,7 +5501,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5606,6 +5666,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5622,11 +5685,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="689166976"/>
-        <c:axId val="691360128"/>
+        <c:axId val="662116224"/>
+        <c:axId val="97841152"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="689166976"/>
+        <c:axId val="662116224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5669,14 +5732,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691360128"/>
+        <c:crossAx val="97841152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="691360128"/>
+        <c:axId val="97841152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5727,12 +5790,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="689166976"/>
+        <c:crossAx val="662116224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="691362048"/>
+        <c:axId val="97842688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5769,12 +5832,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433459200"/>
+        <c:crossAx val="97844224"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="433459200"/>
+        <c:axId val="97844224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5783,7 +5846,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="691362048"/>
+        <c:crossAx val="97842688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5933,7 +5996,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6098,6 +6161,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6107,7 +6173,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6271,6 +6337,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6314,7 +6383,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6479,6 +6548,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6488,7 +6560,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6653,6 +6725,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15173385.354710398</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15282313.065362198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6695,7 +6770,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6860,6 +6935,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6869,7 +6947,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7034,6 +7112,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5210599.9754604883</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5319527.6861122884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7055,11 +7136,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433511424"/>
-        <c:axId val="433513216"/>
+        <c:axId val="155875968"/>
+        <c:axId val="155877760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433511424"/>
+        <c:axId val="155875968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7102,14 +7183,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433513216"/>
+        <c:crossAx val="155877760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433513216"/>
+        <c:axId val="155877760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7160,7 +7241,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433511424"/>
+        <c:crossAx val="155875968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7321,7 +7402,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7486,6 +7567,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7500,8 +7584,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="437153792"/>
-        <c:axId val="437152000"/>
+        <c:axId val="155892736"/>
+        <c:axId val="155891200"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7526,7 +7610,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7691,6 +7775,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7700,7 +7787,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7865,6 +7952,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7881,11 +7971,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437144576"/>
-        <c:axId val="437150464"/>
+        <c:axId val="155887872"/>
+        <c:axId val="155889664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437144576"/>
+        <c:axId val="155887872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7928,14 +8018,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437150464"/>
+        <c:crossAx val="155889664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="437150464"/>
+        <c:axId val="155889664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7986,12 +8076,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437144576"/>
+        <c:crossAx val="155887872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="437152000"/>
+        <c:axId val="155891200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8028,12 +8118,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437153792"/>
+        <c:crossAx val="155892736"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="437153792"/>
+        <c:axId val="155892736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8042,7 +8132,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="437152000"/>
+        <c:crossAx val="155891200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8192,7 +8282,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8357,6 +8447,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8366,7 +8459,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8530,6 +8623,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8573,7 +8669,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8738,6 +8834,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8747,7 +8846,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8912,6 +9011,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>135374422.21281305</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>136361067.73708206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8954,7 +9056,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9119,6 +9221,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9128,7 +9233,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9293,6 +9398,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>47934469.550210342</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>48921115.074479356</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9314,11 +9422,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437181440"/>
-        <c:axId val="437183232"/>
+        <c:axId val="160479488"/>
+        <c:axId val="160485376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437181440"/>
+        <c:axId val="160479488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9361,14 +9469,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437183232"/>
+        <c:crossAx val="160485376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="437183232"/>
+        <c:axId val="160485376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9419,7 +9527,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437181440"/>
+        <c:crossAx val="160479488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9580,7 +9688,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9745,6 +9853,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>123330440.59734799</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>122634814.91739957</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9759,8 +9870,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="447753216"/>
-        <c:axId val="447751680"/>
+        <c:axId val="506735232"/>
+        <c:axId val="506733696"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9785,7 +9896,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9950,6 +10061,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9959,7 +10073,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10124,6 +10238,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10140,11 +10257,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="447744256"/>
-        <c:axId val="447750144"/>
+        <c:axId val="506726272"/>
+        <c:axId val="506727808"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="447744256"/>
+        <c:axId val="506726272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10187,14 +10304,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447750144"/>
+        <c:crossAx val="506727808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447750144"/>
+        <c:axId val="506727808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10245,12 +10362,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447744256"/>
+        <c:crossAx val="506726272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="447751680"/>
+        <c:axId val="506733696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10287,12 +10404,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447753216"/>
+        <c:crossAx val="506735232"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="447753216"/>
+        <c:axId val="506735232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10301,7 +10418,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="447751680"/>
+        <c:crossAx val="506733696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10451,7 +10568,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10616,6 +10733,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10625,7 +10745,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10789,6 +10909,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -10832,7 +10955,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10997,6 +11120,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11006,7 +11132,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11171,6 +11297,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>139607183.83490777</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>140637660.28223953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11213,7 +11342,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11378,6 +11507,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11387,7 +11519,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11552,6 +11684,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>56026187.499287754</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>57056663.946619511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11573,11 +11708,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="452593920"/>
-        <c:axId val="452595712"/>
+        <c:axId val="506754944"/>
+        <c:axId val="506756480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="452593920"/>
+        <c:axId val="506754944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11620,14 +11755,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452595712"/>
+        <c:crossAx val="506756480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="452595712"/>
+        <c:axId val="506756480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11678,7 +11813,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452593920"/>
+        <c:crossAx val="506754944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12392,7 +12527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -14845,6 +14980,44 @@
         <v>628259.51158101915</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>12659943.042425262</v>
+      </c>
+      <c r="H58" s="15">
+        <v>13571459.279536832</v>
+      </c>
+      <c r="I58" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J58" s="15">
+        <v>14329709.596181171</v>
+      </c>
+      <c r="K58" s="15">
+        <v>4968374.7784537468</v>
+      </c>
+      <c r="L58" s="14">
+        <v>758250.31664433924</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -14861,7 +15034,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18633,6 +18806,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="58" spans="1:21" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>13544471.519235244</v>
+      </c>
+      <c r="H58" s="15">
+        <v>14519673.830296591</v>
+      </c>
+      <c r="I58" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J58" s="15">
+        <v>15403573.839066558</v>
+      </c>
+      <c r="K58" s="15">
+        <v>5395800.2995436862</v>
+      </c>
+      <c r="L58" s="14">
+        <v>883900.00876996701</v>
+      </c>
+      <c r="M58" s="23">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="N58" s="23">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="O58" s="23">
+        <v>1.0756666660308838</v>
+      </c>
+      <c r="P58" s="23">
+        <v>0.904595238821847</v>
+      </c>
+      <c r="Q58" s="23">
+        <v>0.17107142720903679</v>
+      </c>
+      <c r="R58" s="23">
+        <v>0.11863264907785012</v>
+      </c>
+      <c r="S58" s="9">
+        <v>1.7794897361677517E-3</v>
+      </c>
+      <c r="T58" s="9">
+        <v>96.135101952006963</v>
+      </c>
+      <c r="U58" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -18649,7 +18887,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21421,6 +21659,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>13494676.161662014</v>
+      </c>
+      <c r="H58" s="15">
+        <v>14466293.205648409</v>
+      </c>
+      <c r="I58" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J58" s="15">
+        <v>15282313.065362198</v>
+      </c>
+      <c r="K58" s="15">
+        <v>5319527.6861122884</v>
+      </c>
+      <c r="L58" s="14">
+        <v>816019.85971378826</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -21437,7 +21719,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24209,6 +24491,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-745710.74747990887</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-695625.6799484134</v>
+      </c>
+      <c r="G58" s="15">
+        <v>122634814.91739957</v>
+      </c>
+      <c r="H58" s="15">
+        <v>131464524.86615519</v>
+      </c>
+      <c r="I58" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J58" s="15">
+        <v>136361067.73708206</v>
+      </c>
+      <c r="K58" s="15">
+        <v>48921115.074479356</v>
+      </c>
+      <c r="L58" s="14">
+        <v>4896542.8709268663</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24225,7 +24551,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -27335,6 +27661,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:16" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="14">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="14">
+        <v>-637497.67999171233</v>
+      </c>
+      <c r="H58" s="15">
+        <v>-594680.65682091936</v>
+      </c>
+      <c r="I58" s="15">
+        <v>128214614.22015479</v>
+      </c>
+      <c r="J58" s="15">
+        <v>137446069.86770549</v>
+      </c>
+      <c r="K58" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L58" s="15">
+        <v>140637660.28223953</v>
+      </c>
+      <c r="M58" s="15">
+        <v>57056663.946619511</v>
+      </c>
+      <c r="N58" s="14">
+        <v>3191590.4145340412</v>
+      </c>
+      <c r="O58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="P58" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -730,6 +730,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -739,7 +742,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -906,6 +909,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -949,7 +955,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1117,6 +1123,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1126,7 +1135,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1294,6 +1303,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14329709.596181171</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14367689.690924622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1336,7 +1348,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1504,6 +1516,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1513,7 +1528,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1681,6 +1696,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4968374.7784537468</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5006354.8731971979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1702,11 +1720,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="493797376"/>
-        <c:axId val="493800064"/>
+        <c:axId val="388578304"/>
+        <c:axId val="396993664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="493797376"/>
+        <c:axId val="388578304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1749,14 +1767,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493800064"/>
+        <c:crossAx val="396993664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493800064"/>
+        <c:axId val="396993664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1807,7 +1825,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493797376"/>
+        <c:crossAx val="388578304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1968,7 +1986,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2136,6 +2154,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-637497.67999171233</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-313710.67019325693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2150,8 +2171,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529598336"/>
-        <c:axId val="529596800"/>
+        <c:axId val="81909248"/>
+        <c:axId val="81907712"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2176,7 +2197,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2344,6 +2365,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2353,7 +2377,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2521,6 +2545,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2537,11 +2564,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529581184"/>
-        <c:axId val="529582720"/>
+        <c:axId val="81900288"/>
+        <c:axId val="81901824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529581184"/>
+        <c:axId val="81900288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2584,14 +2611,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529582720"/>
+        <c:crossAx val="81901824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529582720"/>
+        <c:axId val="81901824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2642,12 +2669,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529581184"/>
+        <c:crossAx val="81900288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529596800"/>
+        <c:axId val="81907712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2684,12 +2711,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529598336"/>
+        <c:crossAx val="81909248"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529598336"/>
+        <c:axId val="81909248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,7 +2725,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529596800"/>
+        <c:crossAx val="81907712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2830,7 +2857,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2998,6 +3025,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3012,8 +3042,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="557295488"/>
-        <c:axId val="557293952"/>
+        <c:axId val="483409920"/>
+        <c:axId val="483329920"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3038,7 +3068,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3206,6 +3236,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3215,7 +3248,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3383,6 +3416,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3399,11 +3435,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543789824"/>
-        <c:axId val="543791744"/>
+        <c:axId val="438347648"/>
+        <c:axId val="483328384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543789824"/>
+        <c:axId val="438347648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3446,14 +3482,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543791744"/>
+        <c:crossAx val="483328384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543791744"/>
+        <c:axId val="483328384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3504,12 +3540,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543789824"/>
+        <c:crossAx val="438347648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="557293952"/>
+        <c:axId val="483329920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3546,12 +3582,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557295488"/>
+        <c:crossAx val="483409920"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="557295488"/>
+        <c:axId val="483409920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3560,7 +3596,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="557293952"/>
+        <c:crossAx val="483329920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3710,7 +3746,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3878,6 +3914,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3887,7 +3926,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4054,6 +4093,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4097,7 +4139,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4265,6 +4307,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4274,7 +4319,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4442,6 +4487,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15403573.839066558</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15444207.537798585</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4484,7 +4532,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4652,6 +4700,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4661,7 +4712,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4829,6 +4880,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5395800.2995436862</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5436433.998275714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4850,11 +4904,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="609127808"/>
-        <c:axId val="610740480"/>
+        <c:axId val="531903232"/>
+        <c:axId val="531904768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="609127808"/>
+        <c:axId val="531903232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4897,14 +4951,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="610740480"/>
+        <c:crossAx val="531904768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="610740480"/>
+        <c:axId val="531904768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4955,7 +5009,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609127808"/>
+        <c:crossAx val="531903232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5116,7 +5170,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5284,6 +5338,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5298,8 +5355,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="97844224"/>
-        <c:axId val="97842688"/>
+        <c:axId val="691714304"/>
+        <c:axId val="691712768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5324,7 +5381,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5492,6 +5549,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5501,7 +5561,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5669,6 +5729,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,11 +5748,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662116224"/>
-        <c:axId val="97841152"/>
+        <c:axId val="623973888"/>
+        <c:axId val="623975424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662116224"/>
+        <c:axId val="623973888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5732,14 +5795,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97841152"/>
+        <c:crossAx val="623975424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="97841152"/>
+        <c:axId val="623975424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5790,12 +5853,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662116224"/>
+        <c:crossAx val="623973888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="97842688"/>
+        <c:axId val="691712768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5832,12 +5895,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97844224"/>
+        <c:crossAx val="691714304"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="97844224"/>
+        <c:axId val="691714304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5846,7 +5909,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="97842688"/>
+        <c:crossAx val="691712768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5996,7 +6059,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6164,6 +6227,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6173,7 +6239,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6340,6 +6406,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6383,7 +6452,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6551,6 +6620,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6560,7 +6632,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6728,6 +6800,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15282313.065362198</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15322797.376976756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6770,7 +6845,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6938,6 +7013,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6947,7 +7025,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7115,6 +7193,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5319527.6861122884</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5360011.9977268465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7136,11 +7217,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="155875968"/>
-        <c:axId val="155877760"/>
+        <c:axId val="76965760"/>
+        <c:axId val="76967296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="155875968"/>
+        <c:axId val="76965760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7183,14 +7264,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155877760"/>
+        <c:crossAx val="76967296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="155877760"/>
+        <c:axId val="76967296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7241,7 +7322,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155875968"/>
+        <c:crossAx val="76965760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7402,7 +7483,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7570,6 +7651,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7584,8 +7668,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="155892736"/>
-        <c:axId val="155891200"/>
+        <c:axId val="76998912"/>
+        <c:axId val="76997376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7610,7 +7694,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7778,6 +7862,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7787,7 +7874,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7955,6 +8042,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7971,11 +8061,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="155887872"/>
-        <c:axId val="155889664"/>
+        <c:axId val="76994048"/>
+        <c:axId val="76995584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="155887872"/>
+        <c:axId val="76994048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8018,14 +8108,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155889664"/>
+        <c:crossAx val="76995584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="155889664"/>
+        <c:axId val="76995584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8076,12 +8166,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155887872"/>
+        <c:crossAx val="76994048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="155891200"/>
+        <c:axId val="76997376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8118,12 +8208,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155892736"/>
+        <c:crossAx val="76998912"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="155892736"/>
+        <c:axId val="76998912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8132,7 +8222,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="155891200"/>
+        <c:crossAx val="76997376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8282,7 +8372,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8450,6 +8540,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8459,7 +8552,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8626,6 +8719,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8669,7 +8765,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8837,6 +8933,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8846,7 +8945,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9014,6 +9113,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>136361067.73708206</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>136728974.75481507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9056,7 +9158,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9224,6 +9326,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9233,7 +9338,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9401,6 +9506,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>48921115.074479356</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>49289022.092212364</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9422,11 +9530,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="160479488"/>
-        <c:axId val="160485376"/>
+        <c:axId val="79152640"/>
+        <c:axId val="79154176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="160479488"/>
+        <c:axId val="79152640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9469,14 +9577,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160485376"/>
+        <c:crossAx val="79154176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160485376"/>
+        <c:axId val="79154176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9527,7 +9635,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160479488"/>
+        <c:crossAx val="79152640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9688,7 +9796,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9856,6 +9964,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>122634814.91739957</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>122020082.29885046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9870,8 +9981,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="506735232"/>
-        <c:axId val="506733696"/>
+        <c:axId val="81868672"/>
+        <c:axId val="81867136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9896,7 +10007,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10064,6 +10175,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10073,7 +10187,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10241,6 +10355,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10257,11 +10374,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="506726272"/>
-        <c:axId val="506727808"/>
+        <c:axId val="81859712"/>
+        <c:axId val="81861248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="506726272"/>
+        <c:axId val="81859712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10304,14 +10421,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506727808"/>
+        <c:crossAx val="81861248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="506727808"/>
+        <c:axId val="81861248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10362,12 +10479,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506726272"/>
+        <c:crossAx val="81859712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="506733696"/>
+        <c:axId val="81867136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10404,12 +10521,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506735232"/>
+        <c:crossAx val="81868672"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="506735232"/>
+        <c:axId val="81868672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10418,7 +10535,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="506733696"/>
+        <c:crossAx val="81867136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10568,7 +10685,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10736,6 +10853,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10745,7 +10865,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10912,6 +11032,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -10955,7 +11078,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11123,6 +11246,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11132,7 +11258,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11300,6 +11426,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>140637660.28223953</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>141022306.81494966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11342,7 +11471,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11510,6 +11639,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11519,7 +11651,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11687,6 +11819,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>57056663.946619511</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57441310.479329646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11708,11 +11843,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="506754944"/>
-        <c:axId val="506756480"/>
+        <c:axId val="81884288"/>
+        <c:axId val="81885824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="506754944"/>
+        <c:axId val="81884288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11755,14 +11890,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506756480"/>
+        <c:crossAx val="81885824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="506756480"/>
+        <c:axId val="81885824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11813,7 +11948,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506754944"/>
+        <c:crossAx val="81884288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12527,7 +12662,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15018,6 +15153,44 @@
         <v>758250.31664433924</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>12548379.99314902</v>
+      </c>
+      <c r="H59" s="15">
+        <v>13489509.090988582</v>
+      </c>
+      <c r="I59" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J59" s="15">
+        <v>14367689.690924622</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5006354.8731971979</v>
+      </c>
+      <c r="L59" s="14">
+        <v>878180.59993604012</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15034,7 +15207,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18871,6 +19044,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:21" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>13432908.469959002</v>
+      </c>
+      <c r="H59" s="15">
+        <v>14440377.245736917</v>
+      </c>
+      <c r="I59" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J59" s="15">
+        <v>15444207.537798585</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5436433.998275714</v>
+      </c>
+      <c r="L59" s="14">
+        <v>1003830.2920616679</v>
+      </c>
+      <c r="M59" s="23">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="N59" s="23">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="O59" s="23">
+        <v>1.071333368619283</v>
+      </c>
+      <c r="P59" s="23">
+        <v>0.92366667020888549</v>
+      </c>
+      <c r="Q59" s="23">
+        <v>0.14766669841039748</v>
+      </c>
+      <c r="R59" s="23">
+        <v>0.1233809505190168</v>
+      </c>
+      <c r="S59" s="9">
+        <v>1.850714257785252E-3</v>
+      </c>
+      <c r="T59" s="9">
+        <v>79.789031607240162</v>
+      </c>
+      <c r="U59" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -18887,7 +19125,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21703,6 +21941,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>13383113.112385772</v>
+      </c>
+      <c r="H59" s="15">
+        <v>14386847.233971268</v>
+      </c>
+      <c r="I59" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J59" s="15">
+        <v>15322797.376976756</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5360011.9977268465</v>
+      </c>
+      <c r="L59" s="14">
+        <v>935950.14300548914</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -21719,7 +22001,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24535,6 +24817,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-660837.59425302898</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-614732.61854911025</v>
+      </c>
+      <c r="G59" s="15">
+        <v>122020082.29885046</v>
+      </c>
+      <c r="H59" s="15">
+        <v>131171594.28963518</v>
+      </c>
+      <c r="I59" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J59" s="15">
+        <v>136728974.75481507</v>
+      </c>
+      <c r="K59" s="15">
+        <v>49289022.092212364</v>
+      </c>
+      <c r="L59" s="14">
+        <v>5557380.4651798951</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24551,7 +24877,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -27711,6 +28037,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:16" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="14">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="14">
+        <v>-313710.67019325693</v>
+      </c>
+      <c r="H59" s="15">
+        <v>-291823.86630512617</v>
+      </c>
+      <c r="I59" s="15">
+        <v>127922790.35384966</v>
+      </c>
+      <c r="J59" s="15">
+        <v>137517005.73022237</v>
+      </c>
+      <c r="K59" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L59" s="15">
+        <v>141022306.81494966</v>
+      </c>
+      <c r="M59" s="15">
+        <v>57441310.479329646</v>
+      </c>
+      <c r="N59" s="14">
+        <v>3505301.084727298</v>
+      </c>
+      <c r="O59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="P59" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -733,6 +733,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -742,7 +745,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -912,6 +915,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -955,7 +961,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1126,6 +1132,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1135,7 +1144,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1306,6 +1315,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14367689.690924622</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14028882.557513656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1348,7 +1360,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1519,6 +1531,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1528,7 +1543,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1699,6 +1714,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5006354.8731971979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4667547.7397862319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,11 +1738,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="388578304"/>
-        <c:axId val="396993664"/>
+        <c:axId val="385507328"/>
+        <c:axId val="385510400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="388578304"/>
+        <c:axId val="385507328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1767,14 +1785,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="396993664"/>
+        <c:crossAx val="385510400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="396993664"/>
+        <c:axId val="385510400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1825,7 +1843,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="388578304"/>
+        <c:crossAx val="385507328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1986,7 +2004,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2157,6 +2175,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-313710.67019325693</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-166564.10795343228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2171,8 +2192,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="81909248"/>
-        <c:axId val="81907712"/>
+        <c:axId val="103291904"/>
+        <c:axId val="103290368"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2197,7 +2218,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2368,6 +2389,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2377,7 +2401,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2548,6 +2572,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2564,11 +2591,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="81900288"/>
-        <c:axId val="81901824"/>
+        <c:axId val="103287040"/>
+        <c:axId val="103288832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="81900288"/>
+        <c:axId val="103287040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2611,14 +2638,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81901824"/>
+        <c:crossAx val="103288832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81901824"/>
+        <c:axId val="103288832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2669,12 +2696,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81900288"/>
+        <c:crossAx val="103287040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81907712"/>
+        <c:axId val="103290368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2711,12 +2738,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81909248"/>
+        <c:crossAx val="103291904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="81909248"/>
+        <c:axId val="103291904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,7 +2752,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81907712"/>
+        <c:crossAx val="103290368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2857,7 +2884,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3028,6 +3055,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3042,8 +3072,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="483409920"/>
-        <c:axId val="483329920"/>
+        <c:axId val="417357184"/>
+        <c:axId val="417354880"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3068,7 +3098,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3239,6 +3269,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3248,7 +3281,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3419,6 +3452,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3435,11 +3471,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438347648"/>
-        <c:axId val="483328384"/>
+        <c:axId val="417240960"/>
+        <c:axId val="417242496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438347648"/>
+        <c:axId val="417240960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3482,14 +3518,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483328384"/>
+        <c:crossAx val="417242496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483328384"/>
+        <c:axId val="417242496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3540,12 +3576,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438347648"/>
+        <c:crossAx val="417240960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="483329920"/>
+        <c:axId val="417354880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3582,12 +3618,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483409920"/>
+        <c:crossAx val="417357184"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="483409920"/>
+        <c:axId val="417357184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3596,7 +3632,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="483329920"/>
+        <c:crossAx val="417354880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3746,7 +3782,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3917,6 +3953,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3926,7 +3965,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4096,6 +4135,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4139,7 +4181,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4310,6 +4352,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4319,7 +4364,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4490,6 +4535,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>15444207.537798585</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15081518.073934447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4532,7 +4580,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4703,6 +4751,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4712,7 +4763,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4883,6 +4934,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5436433.998275714</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5073744.5344115756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4904,11 +4958,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="531903232"/>
-        <c:axId val="531904768"/>
+        <c:axId val="425677184"/>
+        <c:axId val="425679104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="531903232"/>
+        <c:axId val="425677184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4951,14 +5005,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531904768"/>
+        <c:crossAx val="425679104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="531904768"/>
+        <c:axId val="425679104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5009,7 +5063,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531903232"/>
+        <c:crossAx val="425677184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5170,7 +5224,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5341,6 +5395,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5355,8 +5412,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="691714304"/>
-        <c:axId val="691712768"/>
+        <c:axId val="521325952"/>
+        <c:axId val="521324416"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5381,7 +5438,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5552,6 +5609,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5561,7 +5621,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5732,6 +5792,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5748,11 +5811,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623973888"/>
-        <c:axId val="623975424"/>
+        <c:axId val="432777088"/>
+        <c:axId val="521322496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623973888"/>
+        <c:axId val="432777088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5795,14 +5858,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623975424"/>
+        <c:crossAx val="521322496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623975424"/>
+        <c:axId val="521322496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5853,12 +5916,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623973888"/>
+        <c:crossAx val="432777088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="691712768"/>
+        <c:axId val="521324416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5895,12 +5958,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691714304"/>
+        <c:crossAx val="521325952"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="691714304"/>
+        <c:axId val="521325952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5909,7 +5972,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="691712768"/>
+        <c:crossAx val="521324416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6059,7 +6122,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6230,6 +6293,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6239,7 +6305,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6409,6 +6475,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6452,7 +6521,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6623,6 +6692,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6632,7 +6704,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6803,6 +6875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>15322797.376976756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14961452.391233759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6845,7 +6920,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7016,6 +7091,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7025,7 +7103,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7196,6 +7274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5360011.9977268465</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4998667.0119838491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7217,11 +7298,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="76965760"/>
-        <c:axId val="76967296"/>
+        <c:axId val="78994816"/>
+        <c:axId val="78996608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76965760"/>
+        <c:axId val="78994816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7264,14 +7345,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76967296"/>
+        <c:crossAx val="78996608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76967296"/>
+        <c:axId val="78996608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7322,7 +7403,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76965760"/>
+        <c:crossAx val="78994816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7483,7 +7564,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7654,6 +7735,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7668,8 +7752,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="76998912"/>
-        <c:axId val="76997376"/>
+        <c:axId val="79020416"/>
+        <c:axId val="79014528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7694,7 +7778,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7865,6 +7949,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7874,7 +7961,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8045,6 +8132,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8061,11 +8151,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="76994048"/>
-        <c:axId val="76995584"/>
+        <c:axId val="79007104"/>
+        <c:axId val="79012992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76994048"/>
+        <c:axId val="79007104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8108,14 +8198,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76995584"/>
+        <c:crossAx val="79012992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76995584"/>
+        <c:axId val="79012992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8166,12 +8256,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76994048"/>
+        <c:crossAx val="79007104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76997376"/>
+        <c:axId val="79014528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8208,12 +8298,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76998912"/>
+        <c:crossAx val="79020416"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="76998912"/>
+        <c:axId val="79020416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8222,7 +8312,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="76997376"/>
+        <c:crossAx val="79014528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8372,7 +8462,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8543,6 +8633,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8552,7 +8645,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8722,6 +8815,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8765,7 +8861,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8936,6 +9032,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8945,7 +9044,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9116,6 +9215,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>136728974.75481507</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>133434424.03792456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9158,7 +9260,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9329,6 +9431,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9338,7 +9443,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9509,6 +9614,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>49289022.092212364</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>45994471.37532185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9530,11 +9638,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79152640"/>
-        <c:axId val="79154176"/>
+        <c:axId val="79842688"/>
+        <c:axId val="79852672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79152640"/>
+        <c:axId val="79842688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9577,14 +9685,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79154176"/>
+        <c:crossAx val="79852672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79154176"/>
+        <c:axId val="79852672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9635,7 +9743,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79152640"/>
+        <c:crossAx val="79842688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9796,7 +9904,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9967,6 +10075,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>122020082.29885046</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>121696158.60682116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9981,8 +10092,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="81868672"/>
-        <c:axId val="81867136"/>
+        <c:axId val="79876096"/>
+        <c:axId val="79874304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10007,7 +10118,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10178,6 +10289,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10187,7 +10301,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10358,6 +10472,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10374,11 +10491,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="81859712"/>
-        <c:axId val="81861248"/>
+        <c:axId val="79870976"/>
+        <c:axId val="79872768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="81859712"/>
+        <c:axId val="79870976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10421,14 +10538,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81861248"/>
+        <c:crossAx val="79872768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81861248"/>
+        <c:axId val="79872768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10479,12 +10596,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81859712"/>
+        <c:crossAx val="79870976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81867136"/>
+        <c:axId val="79874304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10521,12 +10638,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81868672"/>
+        <c:crossAx val="79876096"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="81868672"/>
+        <c:axId val="79876096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10535,7 +10652,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81867136"/>
+        <c:crossAx val="79874304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10685,7 +10802,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10856,6 +10973,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10865,7 +10985,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11035,6 +11155,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11078,7 +11201,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11249,6 +11372,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11258,7 +11384,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11429,6 +11555,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>141022306.81494966</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>137568382.5696381</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11471,7 +11600,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11642,6 +11771,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11651,7 +11783,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11822,6 +11954,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>57441310.479329646</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>53987386.234018087</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11843,11 +11978,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="81884288"/>
-        <c:axId val="81885824"/>
+        <c:axId val="80075776"/>
+        <c:axId val="80081664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="81884288"/>
+        <c:axId val="80075776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11890,14 +12025,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81885824"/>
+        <c:crossAx val="80081664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81885824"/>
+        <c:axId val="80081664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11948,7 +12083,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81884288"/>
+        <c:crossAx val="80075776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12662,7 +12797,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15191,6 +15326,44 @@
         <v>878180.59993604012</v>
       </c>
     </row>
+    <row r="60" spans="1:12" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>12474978.130078416</v>
+      </c>
+      <c r="H60" s="15">
+        <v>13073776.806689657</v>
+      </c>
+      <c r="I60" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J60" s="15">
+        <v>14028882.557513656</v>
+      </c>
+      <c r="K60" s="15">
+        <v>4667547.7397862319</v>
+      </c>
+      <c r="L60" s="14">
+        <v>955105.75082399882</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15207,7 +15380,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19109,6 +19282,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:21" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>13359506.606888399</v>
+      </c>
+      <c r="H60" s="15">
+        <v>14000762.63098482</v>
+      </c>
+      <c r="I60" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J60" s="15">
+        <v>15081518.073934447</v>
+      </c>
+      <c r="K60" s="15">
+        <v>5073744.5344115756</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1080755.4429496266</v>
+      </c>
+      <c r="M60" s="23">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="N60" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O60" s="23">
+        <v>1.0603333314259846</v>
+      </c>
+      <c r="P60" s="23">
+        <v>0.94423809789475943</v>
+      </c>
+      <c r="Q60" s="23">
+        <v>0.11609523353122519</v>
+      </c>
+      <c r="R60" s="23">
+        <v>0.11939455619474655</v>
+      </c>
+      <c r="S60" s="9">
+        <v>1.7909183429211982E-3</v>
+      </c>
+      <c r="T60" s="9">
+        <v>64.824414798198021</v>
+      </c>
+      <c r="U60" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19125,7 +19363,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21985,6 +22223,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>13309711.249315169</v>
+      </c>
+      <c r="H60" s="15">
+        <v>13948577.097340312</v>
+      </c>
+      <c r="I60" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J60" s="15">
+        <v>14961452.391233759</v>
+      </c>
+      <c r="K60" s="15">
+        <v>4998667.0119838491</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1012875.2938934478</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22001,7 +22283,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24861,6 +25143,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-339472.02214159875</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-323923.69202929962</v>
+      </c>
+      <c r="G60" s="15">
+        <v>121696158.60682116</v>
+      </c>
+      <c r="H60" s="15">
+        <v>127537571.55060306</v>
+      </c>
+      <c r="I60" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J60" s="15">
+        <v>133434424.03792456</v>
+      </c>
+      <c r="K60" s="15">
+        <v>45994471.37532185</v>
+      </c>
+      <c r="L60" s="14">
+        <v>5896852.4873214941</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24877,7 +25203,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -28087,6 +28413,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:16" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="14">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="14">
+        <v>-166564.10795343228</v>
+      </c>
+      <c r="H60" s="15">
+        <v>-158935.2208393114</v>
+      </c>
+      <c r="I60" s="15">
+        <v>127763855.13301036</v>
+      </c>
+      <c r="J60" s="15">
+        <v>133896517.37695739</v>
+      </c>
+      <c r="K60" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L60" s="15">
+        <v>137568382.5696381</v>
+      </c>
+      <c r="M60" s="15">
+        <v>53987386.234018087</v>
+      </c>
+      <c r="N60" s="14">
+        <v>3671865.1926807305</v>
+      </c>
+      <c r="O60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="P60" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -736,6 +736,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -745,7 +748,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -918,6 +921,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -961,7 +967,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1135,6 +1141,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1144,7 +1153,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1318,6 +1327,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14028882.557513656</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15638155.580985475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1360,7 +1372,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1534,6 +1546,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1543,7 +1558,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1717,6 +1732,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4667547.7397862319</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6276820.7632580511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1738,11 +1756,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="385507328"/>
-        <c:axId val="385510400"/>
+        <c:axId val="463888768"/>
+        <c:axId val="463890304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="385507328"/>
+        <c:axId val="463888768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1785,14 +1803,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385510400"/>
+        <c:crossAx val="463890304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="385510400"/>
+        <c:axId val="463890304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1843,7 +1861,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385507328"/>
+        <c:crossAx val="463888768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2004,7 +2022,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2178,6 +2196,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-166564.10795343228</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-848400.08660027001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2192,8 +2213,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="103291904"/>
-        <c:axId val="103290368"/>
+        <c:axId val="460904704"/>
+        <c:axId val="460903168"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2218,7 +2239,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2392,6 +2413,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2401,7 +2425,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2575,6 +2599,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2591,11 +2618,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="103287040"/>
-        <c:axId val="103288832"/>
+        <c:axId val="460895744"/>
+        <c:axId val="460897280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="103287040"/>
+        <c:axId val="460895744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2638,14 +2665,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103288832"/>
+        <c:crossAx val="460897280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103288832"/>
+        <c:axId val="460897280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2696,12 +2723,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103287040"/>
+        <c:crossAx val="460895744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103290368"/>
+        <c:axId val="460903168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2738,12 +2765,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103291904"/>
+        <c:crossAx val="460904704"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="103291904"/>
+        <c:axId val="460904704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,7 +2779,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103290368"/>
+        <c:crossAx val="460903168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2884,7 +2911,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3058,6 +3085,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3072,8 +3102,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="417357184"/>
-        <c:axId val="417354880"/>
+        <c:axId val="479005312"/>
+        <c:axId val="479003392"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3098,7 +3128,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3272,6 +3302,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3281,7 +3314,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3455,6 +3488,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3471,11 +3507,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="417240960"/>
-        <c:axId val="417242496"/>
+        <c:axId val="478156288"/>
+        <c:axId val="478157824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="417240960"/>
+        <c:axId val="478156288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3518,14 +3554,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417242496"/>
+        <c:crossAx val="478157824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="417242496"/>
+        <c:axId val="478157824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3576,12 +3612,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417240960"/>
+        <c:crossAx val="478156288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="417354880"/>
+        <c:axId val="479003392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3618,12 +3654,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417357184"/>
+        <c:crossAx val="479005312"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="417357184"/>
+        <c:axId val="479005312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3632,7 +3668,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="417354880"/>
+        <c:crossAx val="479003392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3782,7 +3818,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3956,6 +3992,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3965,7 +4004,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4138,6 +4177,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4181,7 +4223,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4355,6 +4397,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4364,7 +4409,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4538,6 +4583,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>15081518.073934447</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16804895.330806952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4580,7 +4628,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4754,6 +4802,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4763,7 +4814,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4937,6 +4988,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5073744.5344115756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6797121.7912840806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4958,11 +5012,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="425677184"/>
-        <c:axId val="425679104"/>
+        <c:axId val="458517120"/>
+        <c:axId val="458518912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="425677184"/>
+        <c:axId val="458517120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5005,14 +5059,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425679104"/>
+        <c:crossAx val="458518912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="425679104"/>
+        <c:axId val="458518912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5063,7 +5117,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425677184"/>
+        <c:crossAx val="458517120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5224,7 +5278,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5398,6 +5452,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5412,8 +5469,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="521325952"/>
-        <c:axId val="521324416"/>
+        <c:axId val="458550272"/>
+        <c:axId val="458548736"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5438,7 +5495,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5612,6 +5669,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5621,7 +5681,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5795,6 +5855,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5811,11 +5874,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="432777088"/>
-        <c:axId val="521322496"/>
+        <c:axId val="458537216"/>
+        <c:axId val="458547200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="432777088"/>
+        <c:axId val="458537216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5858,14 +5921,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521322496"/>
+        <c:crossAx val="458547200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521322496"/>
+        <c:axId val="458547200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5916,12 +5979,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432777088"/>
+        <c:crossAx val="458537216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="521324416"/>
+        <c:axId val="458548736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5958,12 +6021,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521325952"/>
+        <c:crossAx val="458550272"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="521325952"/>
+        <c:axId val="458550272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5972,7 +6035,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="521324416"/>
+        <c:crossAx val="458548736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6122,7 +6185,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6296,6 +6359,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6305,7 +6371,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6478,6 +6544,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6521,7 +6590,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6695,6 +6764,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6704,7 +6776,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6878,6 +6950,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14961452.391233759</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16678406.043607632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6920,7 +6995,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7094,6 +7169,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7103,7 +7181,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7277,6 +7355,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4998667.0119838491</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6715620.6643577218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7298,11 +7379,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78994816"/>
-        <c:axId val="78996608"/>
+        <c:axId val="458746496"/>
+        <c:axId val="458748288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78994816"/>
+        <c:axId val="458746496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7345,14 +7426,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78996608"/>
+        <c:crossAx val="458748288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78996608"/>
+        <c:axId val="458748288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7403,7 +7484,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78994816"/>
+        <c:crossAx val="458746496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7564,7 +7645,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7738,6 +7819,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7752,8 +7836,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="79020416"/>
-        <c:axId val="79014528"/>
+        <c:axId val="459492352"/>
+        <c:axId val="459490816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7778,7 +7862,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7952,6 +8036,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7961,7 +8048,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8135,6 +8222,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8151,11 +8241,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79007104"/>
-        <c:axId val="79012992"/>
+        <c:axId val="459483392"/>
+        <c:axId val="459489280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79007104"/>
+        <c:axId val="459483392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8198,14 +8288,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79012992"/>
+        <c:crossAx val="459489280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79012992"/>
+        <c:axId val="459489280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8256,12 +8346,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79007104"/>
+        <c:crossAx val="459483392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79014528"/>
+        <c:axId val="459490816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8298,12 +8388,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79020416"/>
+        <c:crossAx val="459492352"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="79020416"/>
+        <c:axId val="459492352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8312,7 +8402,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79014528"/>
+        <c:crossAx val="459490816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8462,7 +8552,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8636,6 +8726,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8645,7 +8738,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8818,6 +8911,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8861,7 +8957,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9035,6 +9131,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9044,7 +9143,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9218,6 +9317,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>133434424.03792456</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>149133236.73835805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9260,7 +9362,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9434,6 +9536,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9443,7 +9548,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9617,6 +9722,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>45994471.37532185</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>61693284.075755343</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9638,11 +9746,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79842688"/>
-        <c:axId val="79852672"/>
+        <c:axId val="459516160"/>
+        <c:axId val="459522048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79842688"/>
+        <c:axId val="459516160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9685,14 +9793,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79852672"/>
+        <c:crossAx val="459522048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79852672"/>
+        <c:axId val="459522048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9743,7 +9851,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79842688"/>
+        <c:crossAx val="459516160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9904,7 +10012,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10078,6 +10186,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>121696158.60682116</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>119779016.08311573</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10092,8 +10203,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="79876096"/>
-        <c:axId val="79874304"/>
+        <c:axId val="459618944"/>
+        <c:axId val="459617408"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10118,7 +10229,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10292,6 +10403,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10301,7 +10415,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10475,6 +10589,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10491,11 +10608,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79870976"/>
-        <c:axId val="79872768"/>
+        <c:axId val="459605888"/>
+        <c:axId val="459607424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79870976"/>
+        <c:axId val="459605888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10538,14 +10655,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79872768"/>
+        <c:crossAx val="459607424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79872768"/>
+        <c:axId val="459607424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10596,12 +10713,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79870976"/>
+        <c:crossAx val="459605888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79874304"/>
+        <c:axId val="459617408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10638,12 +10755,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79876096"/>
+        <c:crossAx val="459618944"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="79876096"/>
+        <c:axId val="459618944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10652,7 +10769,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79874304"/>
+        <c:crossAx val="459617408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10802,7 +10919,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10976,6 +11093,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10985,7 +11105,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11158,6 +11278,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11201,7 +11324,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11375,6 +11498,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11384,7 +11510,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11558,6 +11684,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>137568382.5696381</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>154049928.53279907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11600,7 +11729,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11774,6 +11903,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11783,7 +11915,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11957,6 +12089,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>53987386.234018087</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>70468932.197179049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11978,11 +12113,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80075776"/>
-        <c:axId val="80081664"/>
+        <c:axId val="460875648"/>
+        <c:axId val="460877184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80075776"/>
+        <c:axId val="460875648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12025,14 +12160,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80081664"/>
+        <c:crossAx val="460877184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80081664"/>
+        <c:axId val="460877184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12083,7 +12218,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80075776"/>
+        <c:crossAx val="460875648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12797,7 +12932,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15364,6 +15499,44 @@
         <v>955105.75082399882</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>12243926.091061944</v>
+      </c>
+      <c r="H61" s="15">
+        <v>14411101.569662364</v>
+      </c>
+      <c r="I61" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J61" s="15">
+        <v>15638155.580985475</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6276820.7632580511</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1227054.0113231102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15380,7 +15553,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19347,6 +19520,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:21" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>13128454.567871926</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15452191.627358215</v>
+      </c>
+      <c r="I61" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J61" s="15">
+        <v>16804895.330806952</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6797121.7912840806</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1352703.703448738</v>
+      </c>
+      <c r="M61" s="23">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="N61" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O61" s="23">
+        <v>1.1330000162124634</v>
+      </c>
+      <c r="P61" s="23">
+        <v>0.9662142892678578</v>
+      </c>
+      <c r="Q61" s="23">
+        <v>0.16678572694460558</v>
+      </c>
+      <c r="R61" s="23">
+        <v>0.11951701130185809</v>
+      </c>
+      <c r="S61" s="9">
+        <v>1.7927551695278712E-3</v>
+      </c>
+      <c r="T61" s="9">
+        <v>93.033187007085431</v>
+      </c>
+      <c r="U61" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19363,7 +19601,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22267,6 +22505,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>13078659.210298697</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15393582.489215072</v>
+      </c>
+      <c r="I61" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J61" s="15">
+        <v>16678406.043607632</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6715620.6643577218</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1284823.5543925592</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22283,7 +22565,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25187,6 +25469,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-2256476.8381611248</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-1917142.5237054415</v>
+      </c>
+      <c r="G61" s="15">
+        <v>119779016.08311573</v>
+      </c>
+      <c r="H61" s="15">
+        <v>140979907.41287544</v>
+      </c>
+      <c r="I61" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J61" s="15">
+        <v>149133236.73835805</v>
+      </c>
+      <c r="K61" s="15">
+        <v>61693284.075755343</v>
+      </c>
+      <c r="L61" s="14">
+        <v>8153329.325482619</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25203,7 +25529,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -28463,6 +28789,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:16" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="14">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="14">
+        <v>-848400.08660027001</v>
+      </c>
+      <c r="H61" s="15">
+        <v>-720815.67850802618</v>
+      </c>
+      <c r="I61" s="15">
+        <v>127043039.45450233</v>
+      </c>
+      <c r="J61" s="15">
+        <v>149529663.25351807</v>
+      </c>
+      <c r="K61" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L61" s="15">
+        <v>154049928.53279907</v>
+      </c>
+      <c r="M61" s="15">
+        <v>70468932.197179049</v>
+      </c>
+      <c r="N61" s="14">
+        <v>4520265.2792810006</v>
+      </c>
+      <c r="O61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="P61" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI).xlsx
@@ -562,7 +562,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -739,6 +739,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -748,7 +751,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -924,6 +927,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -967,7 +973,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1144,6 +1150,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1153,7 +1162,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1330,6 +1339,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15638155.580985475</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16470742.053078819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1372,7 +1384,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1549,6 +1561,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1558,7 +1573,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1735,6 +1750,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6276820.7632580511</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7109407.2353513949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1756,11 +1774,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463888768"/>
-        <c:axId val="463890304"/>
+        <c:axId val="99720192"/>
+        <c:axId val="103724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463888768"/>
+        <c:axId val="99720192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1803,14 +1821,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463890304"/>
+        <c:crossAx val="103724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="463890304"/>
+        <c:axId val="103724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1861,7 +1879,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463888768"/>
+        <c:crossAx val="99720192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2022,7 +2040,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2199,6 +2217,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-848400.08660027001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-2500093.7589145182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2213,8 +2234,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="460904704"/>
-        <c:axId val="460903168"/>
+        <c:axId val="426328832"/>
+        <c:axId val="426322944"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2239,7 +2260,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2416,6 +2437,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2425,7 +2449,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2602,6 +2626,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,11 +2645,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460895744"/>
-        <c:axId val="460897280"/>
+        <c:axId val="426319872"/>
+        <c:axId val="426321408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460895744"/>
+        <c:axId val="426319872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2665,14 +2692,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460897280"/>
+        <c:crossAx val="426321408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460897280"/>
+        <c:axId val="426321408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,12 +2750,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460895744"/>
+        <c:crossAx val="426319872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="460903168"/>
+        <c:axId val="426322944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2765,12 +2792,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460904704"/>
+        <c:crossAx val="426328832"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="460904704"/>
+        <c:axId val="426328832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2779,7 +2806,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="460903168"/>
+        <c:crossAx val="426322944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2911,7 +2938,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3088,6 +3115,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3102,8 +3132,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="479005312"/>
-        <c:axId val="479003392"/>
+        <c:axId val="424745216"/>
+        <c:axId val="399842304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3128,7 +3158,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3305,6 +3335,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3314,7 +3347,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3491,6 +3524,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3507,11 +3543,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="478156288"/>
-        <c:axId val="478157824"/>
+        <c:axId val="399531392"/>
+        <c:axId val="399840384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="478156288"/>
+        <c:axId val="399531392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3554,14 +3590,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478157824"/>
+        <c:crossAx val="399840384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="478157824"/>
+        <c:axId val="399840384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3612,12 +3648,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478156288"/>
+        <c:crossAx val="399531392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="479003392"/>
+        <c:axId val="399842304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3654,12 +3690,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479005312"/>
+        <c:crossAx val="424745216"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="479005312"/>
+        <c:axId val="424745216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3668,7 +3704,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="479003392"/>
+        <c:crossAx val="399842304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3818,7 +3854,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3995,6 +4031,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4004,7 +4043,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4180,6 +4219,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4223,7 +4265,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4400,6 +4442,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4409,7 +4454,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4586,6 +4631,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16804895.330806952</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17697629.703050636</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4628,7 +4676,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4805,6 +4853,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4814,7 +4865,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4991,6 +5042,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6797121.7912840806</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7689856.1635277644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5012,11 +5066,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458517120"/>
-        <c:axId val="458518912"/>
+        <c:axId val="448737280"/>
+        <c:axId val="448739200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458517120"/>
+        <c:axId val="448737280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5059,14 +5113,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458518912"/>
+        <c:crossAx val="448739200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458518912"/>
+        <c:axId val="448739200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5117,7 +5171,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458517120"/>
+        <c:crossAx val="448737280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5278,7 +5332,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5455,6 +5509,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-394977.32401696721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5469,8 +5526,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="458550272"/>
-        <c:axId val="458548736"/>
+        <c:axId val="605799168"/>
+        <c:axId val="559991424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5495,7 +5552,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5672,6 +5729,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5681,7 +5741,7 @@
               <c:f>'model4(1)&amp;CCI_per_month'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5858,6 +5918,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5874,11 +5937,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458537216"/>
-        <c:axId val="458547200"/>
+        <c:axId val="524069888"/>
+        <c:axId val="559989504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458537216"/>
+        <c:axId val="524069888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5921,14 +5984,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458547200"/>
+        <c:crossAx val="559989504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458547200"/>
+        <c:axId val="559989504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5979,12 +6042,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458537216"/>
+        <c:crossAx val="524069888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="458548736"/>
+        <c:axId val="559991424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6021,12 +6084,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458550272"/>
+        <c:crossAx val="605799168"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="458550272"/>
+        <c:axId val="605799168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6035,7 +6098,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="458548736"/>
+        <c:crossAx val="559991424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6185,7 +6248,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6362,6 +6425,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6371,7 +6437,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6547,6 +6613,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6590,7 +6659,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6767,6 +6836,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6776,7 +6848,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6953,6 +7025,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16678406.043607632</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17567754.333578344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6995,7 +7070,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7172,6 +7247,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7181,7 +7259,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7358,6 +7436,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6715620.6643577218</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7604968.9543284345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7379,11 +7460,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458746496"/>
-        <c:axId val="458748288"/>
+        <c:axId val="99914880"/>
+        <c:axId val="99916416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458746496"/>
+        <c:axId val="99914880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7426,14 +7507,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458748288"/>
+        <c:crossAx val="99916416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458748288"/>
+        <c:axId val="99916416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7484,7 +7565,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458746496"/>
+        <c:crossAx val="99914880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7645,7 +7726,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7822,6 +7903,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-394977.32401696721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7836,8 +7920,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="459492352"/>
-        <c:axId val="459490816"/>
+        <c:axId val="399443840"/>
+        <c:axId val="399442304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7862,7 +7946,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8039,6 +8123,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8048,7 +8135,7 @@
               <c:f>'model4(1)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8225,6 +8312,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8241,11 +8331,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459483392"/>
-        <c:axId val="459489280"/>
+        <c:axId val="374875264"/>
+        <c:axId val="374876800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459483392"/>
+        <c:axId val="374875264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8288,14 +8378,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459489280"/>
+        <c:crossAx val="374876800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459489280"/>
+        <c:axId val="374876800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8346,12 +8436,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459483392"/>
+        <c:crossAx val="374875264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="459490816"/>
+        <c:axId val="399442304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8388,12 +8478,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459492352"/>
+        <c:crossAx val="399443840"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="459492352"/>
+        <c:axId val="399443840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8402,7 +8492,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="459490816"/>
+        <c:crossAx val="399442304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8552,7 +8642,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8729,6 +8819,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8738,7 +8831,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8914,6 +9007,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -8957,7 +9053,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9134,6 +9230,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9143,7 +9242,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9320,6 +9419,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>149133236.73835805</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>157278204.92011258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9362,7 +9464,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9539,6 +9641,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9548,7 +9653,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9725,6 +9830,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>61693284.075755343</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>69838252.257509872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9746,11 +9854,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459516160"/>
-        <c:axId val="459522048"/>
+        <c:axId val="399463168"/>
+        <c:axId val="399464704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459516160"/>
+        <c:axId val="399463168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9793,14 +9901,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459522048"/>
+        <c:crossAx val="399464704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459522048"/>
+        <c:axId val="399464704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9851,7 +9959,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459516160"/>
+        <c:crossAx val="399463168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10012,7 +10120,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10189,6 +10297,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>119779016.08311573</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>116883008.32632542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10203,8 +10314,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="459618944"/>
-        <c:axId val="459617408"/>
+        <c:axId val="399484032"/>
+        <c:axId val="399482240"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10229,7 +10340,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10406,6 +10517,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10415,7 +10529,7 @@
               <c:f>'model4(3)&amp;CCI_per_day'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10592,6 +10706,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10608,11 +10725,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459605888"/>
-        <c:axId val="459607424"/>
+        <c:axId val="399479168"/>
+        <c:axId val="399480704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459605888"/>
+        <c:axId val="399479168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10655,14 +10772,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459607424"/>
+        <c:crossAx val="399480704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459607424"/>
+        <c:axId val="399480704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10713,12 +10830,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459605888"/>
+        <c:crossAx val="399479168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="459617408"/>
+        <c:axId val="399482240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10755,12 +10872,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459618944"/>
+        <c:crossAx val="399484032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="459618944"/>
+        <c:axId val="399484032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10769,7 +10886,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="459617408"/>
+        <c:crossAx val="399482240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10919,7 +11036,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11096,6 +11213,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11105,7 +11225,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11281,6 +11401,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11324,7 +11447,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11501,6 +11624,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11510,7 +11636,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11687,6 +11813,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>154049928.53279907</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>162688850.00592482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11729,7 +11858,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11906,6 +12035,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11915,7 +12047,7 @@
               <c:f>'model4(3)vol&amp;CCI_per_day'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12092,6 +12224,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>70468932.197179049</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>79107853.670304805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12113,11 +12248,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460875648"/>
-        <c:axId val="460877184"/>
+        <c:axId val="401916288"/>
+        <c:axId val="401917824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460875648"/>
+        <c:axId val="401916288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12160,14 +12295,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460877184"/>
+        <c:crossAx val="401917824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460877184"/>
+        <c:axId val="401917824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12218,7 +12353,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460875648"/>
+        <c:crossAx val="401916288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12932,7 +13067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15537,6 +15672,44 @@
         <v>1227054.0113231102</v>
       </c>
     </row>
+    <row r="62" spans="1:12" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="15">
+        <v>11979550.373187648</v>
+      </c>
+      <c r="H62" s="15">
+        <v>14914540.271741569</v>
+      </c>
+      <c r="I62" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J62" s="15">
+        <v>16470742.053078819</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7109407.2353513949</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1556201.7813372496</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15553,7 +15726,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19585,6 +19758,71 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:21" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-394977.32401696721</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-317250.86144915438</v>
+      </c>
+      <c r="G62" s="15">
+        <v>12811203.706422772</v>
+      </c>
+      <c r="H62" s="15">
+        <v>15949948.675584931</v>
+      </c>
+      <c r="I62" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J62" s="15">
+        <v>17697629.703050636</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7689856.1635277644</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1747681.0274657053</v>
+      </c>
+      <c r="M62" s="23">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="N62" s="23">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="O62" s="23">
+        <v>1.2263333400090535</v>
+      </c>
+      <c r="P62" s="23">
+        <v>0.9948571466264271</v>
+      </c>
+      <c r="Q62" s="23">
+        <v>0.23147619338262637</v>
+      </c>
+      <c r="R62" s="23">
+        <v>0.11985034480386848</v>
+      </c>
+      <c r="S62" s="9">
+        <v>1.7977551720580272E-3</v>
+      </c>
+      <c r="T62" s="9">
+        <v>128.75846332158676</v>
+      </c>
+      <c r="U62" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19601,7 +19839,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22549,6 +22787,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-394977.32401696721</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-317250.86144915438</v>
+      </c>
+      <c r="G62" s="15">
+        <v>12761408.348849542</v>
+      </c>
+      <c r="H62" s="15">
+        <v>15887953.455168817</v>
+      </c>
+      <c r="I62" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J62" s="15">
+        <v>17567754.333578344</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7604968.9543284345</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1679800.8784095263</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22565,7 +22847,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25513,6 +25795,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-3605529.6710131839</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-2896007.7567903157</v>
+      </c>
+      <c r="G62" s="15">
+        <v>116883008.32632542</v>
+      </c>
+      <c r="H62" s="15">
+        <v>145519345.92361677</v>
+      </c>
+      <c r="I62" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J62" s="15">
+        <v>157278204.92011258</v>
+      </c>
+      <c r="K62" s="15">
+        <v>69838252.257509872</v>
+      </c>
+      <c r="L62" s="14">
+        <v>11758858.996495802</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25529,7 +25855,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -28839,6 +29165,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:16" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="14">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="14">
+        <v>-2500093.7589145182</v>
+      </c>
+      <c r="H62" s="15">
+        <v>-2008107.4291880447</v>
+      </c>
+      <c r="I62" s="15">
+        <v>125034932.02531429</v>
+      </c>
+      <c r="J62" s="15">
+        <v>155668490.9677293</v>
+      </c>
+      <c r="K62" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L62" s="15">
+        <v>162688850.00592482</v>
+      </c>
+      <c r="M62" s="15">
+        <v>79107853.670304805</v>
+      </c>
+      <c r="N62" s="14">
+        <v>7020359.0381955188</v>
+      </c>
+      <c r="O62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="P62" s="9">
+        <v>1.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J2">
